--- a/Financials/Transaction Tax/Manage Taxes/Manage Taxes_Excel.xlsx
+++ b/Financials/Transaction Tax/Manage Taxes/Manage Taxes_Excel.xlsx
@@ -10,37 +10,55 @@
     <sheet name="Doc" sheetId="1" r:id="rId1"/>
     <sheet name="Parmeters" sheetId="2" r:id="rId2"/>
     <sheet name="TaxRegime" sheetId="3" r:id="rId3"/>
-    <sheet name="Taxes" sheetId="4" r:id="rId4"/>
-    <sheet name="XDO_METADATA" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Tax" sheetId="4" r:id="rId4"/>
+    <sheet name="DefaultTaxStatus" sheetId="5" r:id="rId5"/>
+    <sheet name="DefaultTaxRate" sheetId="6" r:id="rId6"/>
+    <sheet name="XDO_METADATA" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="XDO_?XDOFIELD22?">Taxes!$C$3:$C$49</definedName>
-    <definedName name="XDO_?XDOFIELD3?">TaxRegime!$B$3</definedName>
-    <definedName name="XDO_?XDOFIELD25?">Taxes!$F$3:$F$49</definedName>
-    <definedName name="XDO_?XDOFIELD6?">TaxRegime!$E$3</definedName>
-    <definedName name="XDO_?XDOFIELD9?">TaxRegime!$H$3</definedName>
+    <definedName name="XDO_?XDOFIELD32?">DefaultTaxStatus!$E$3:$E$49</definedName>
+    <definedName name="XDO_?XDOFIELD35?">DefaultTaxRate!$B$3:$B$51</definedName>
+    <definedName name="XDO_?XDOFIELD38?">DefaultTaxRate!$E$3:$E$51</definedName>
+    <definedName name="XDO_GROUP_?XDOG2?">Tax!$A$3:$CA$49</definedName>
+    <definedName name="XDO_?XDOFIELD22?">Tax!$C$3:$C$49</definedName>
+    <definedName name="XDO_?XDOFIELD25?">Tax!$F$3:$F$49</definedName>
+    <definedName name="XDO_?XDOFIELD28?">DefaultTaxStatus!$A$3:$A$49</definedName>
+    <definedName name="XDO_?XDOFIELD41?">DefaultTaxRate!$H$3:$H$51</definedName>
+    <definedName name="XDO_?XDOFIELD2?">TaxRegime!$A$3</definedName>
+    <definedName name="XDO_?XDOFIELD5?">TaxRegime!$D$3</definedName>
+    <definedName name="XDO_?XDOFIELD12?">TaxRegime!$K$3</definedName>
+    <definedName name="XDO_?XDOFIELD8?">TaxRegime!$G$3</definedName>
+    <definedName name="XDO_?XDOFIELD15?">TaxRegime!$N$3</definedName>
+    <definedName name="XDO_?XDOFIELD18?">TaxRegime!$Q$3</definedName>
+    <definedName name="XDO_?XDOFIELD31?">DefaultTaxStatus!$D$3:$D$49</definedName>
+    <definedName name="XDO_?XDOFIELD34?">DefaultTaxRate!$A$3:$A$51</definedName>
+    <definedName name="XDO_?XDOFIELD37?">DefaultTaxRate!$D$3:$D$51</definedName>
+    <definedName name="XDO_GROUP_?XDOG1?">TaxRegime!$A$3:$CA$3</definedName>
+    <definedName name="XDO_?XDOFIELD21?">Tax!$B$3:$B$49</definedName>
+    <definedName name="XDO_GROUP_?XDOG4?">DefaultTaxRate!$A$3:$CA$51</definedName>
+    <definedName name="XDO_?XDOFIELD24?">Tax!$E$3:$E$49</definedName>
+    <definedName name="XDO_?XDOFIELD27?">Tax!$H$3:$H$49</definedName>
+    <definedName name="XDO_?XDOFIELD40?">DefaultTaxRate!$G$3:$G$51</definedName>
+    <definedName name="XDO_?XDOFIELD1?">Parmeters!$B$3</definedName>
+    <definedName name="XDO_?XDOFIELD4?">TaxRegime!$C$3</definedName>
     <definedName name="XDO_?XDOFIELD11?">TaxRegime!$J$3</definedName>
-    <definedName name="XDO_GROUP_?XDOG2?">Taxes!$A$3:$CA$49</definedName>
+    <definedName name="XDO_?XDOFIELD7?">TaxRegime!$F$3</definedName>
     <definedName name="XDO_?XDOFIELD14?">TaxRegime!$M$3</definedName>
     <definedName name="XDO_?XDOFIELD17?">TaxRegime!$P$3</definedName>
-    <definedName name="XDO_?XDOFIELD20?">Taxes!$A$3:$A$49</definedName>
-    <definedName name="XDO_?XDOFIELD1?">Parmeters!$B$3</definedName>
-    <definedName name="XDO_?XDOFIELD23?">Taxes!$D$3:$D$49</definedName>
-    <definedName name="XDO_?XDOFIELD4?">TaxRegime!$C$3</definedName>
-    <definedName name="XDO_?XDOFIELD26?">Taxes!$G$3:$G$49</definedName>
-    <definedName name="XDO_?XDOFIELD7?">TaxRegime!$F$3</definedName>
-    <definedName name="XDO_?XDOFIELD12?">TaxRegime!$K$3</definedName>
-    <definedName name="XDO_?XDOFIELD15?">TaxRegime!$N$3</definedName>
-    <definedName name="XDO_?XDOFIELD18?">TaxRegime!$Q$3</definedName>
-    <definedName name="XDO_?XDOFIELD21?">Taxes!$B$3:$B$49</definedName>
-    <definedName name="XDO_?XDOFIELD24?">Taxes!$E$3:$E$49</definedName>
-    <definedName name="XDO_?XDOFIELD2?">TaxRegime!$A$3</definedName>
-    <definedName name="XDO_?XDOFIELD5?">TaxRegime!$D$3</definedName>
-    <definedName name="XDO_?XDOFIELD27?">Taxes!$H$3:$H$49</definedName>
-    <definedName name="XDO_?XDOFIELD8?">TaxRegime!$G$3</definedName>
+    <definedName name="XDO_?XDOFIELD30?">DefaultTaxStatus!$C$3:$C$49</definedName>
+    <definedName name="XDO_?XDOFIELD33?">DefaultTaxStatus!$F$3:$F$49</definedName>
+    <definedName name="XDO_?XDOFIELD36?">DefaultTaxRate!$C$3:$C$51</definedName>
+    <definedName name="XDO_?XDOFIELD39?">DefaultTaxRate!$F$3:$F$51</definedName>
+    <definedName name="XDO_?XDOFIELD20?">Tax!$A$3:$A$49</definedName>
+    <definedName name="XDO_GROUP_?XDOG3?">DefaultTaxStatus!$A$3:$CA$49</definedName>
+    <definedName name="XDO_?XDOFIELD23?">Tax!$D$3:$D$49</definedName>
+    <definedName name="XDO_?XDOFIELD26?">Tax!$G$3:$G$49</definedName>
+    <definedName name="XDO_?XDOFIELD29?">DefaultTaxStatus!$B$3:$B$49</definedName>
     <definedName name="XDO_?XDOFIELD10?">TaxRegime!$I$3</definedName>
-    <definedName name="XDO_GROUP_?XDOG1?">TaxRegime!$A$3:$CA$3</definedName>
+    <definedName name="XDO_?XDOFIELD3?">TaxRegime!$B$3</definedName>
+    <definedName name="XDO_?XDOFIELD6?">TaxRegime!$E$3</definedName>
     <definedName name="XDO_?XDOFIELD13?">TaxRegime!$L$3</definedName>
+    <definedName name="XDO_?XDOFIELD9?">TaxRegime!$H$3</definedName>
     <definedName name="XDO_?XDOFIELD16?">TaxRegime!$O$3</definedName>
     <definedName name="XDO_?XDOFIELD19?">Parmeters!$B$4</definedName>
   </definedNames>
@@ -49,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t>Version</t>
   </si>
@@ -84,9 +102,6 @@
     <t>www.linkedin.com/in/cristian-arakaki</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/cristian-arakaki/</t>
-  </si>
-  <si>
     <t>26C</t>
   </si>
   <si>
@@ -132,139 +147,88 @@
     <t>XDO_?XDOFIELD2?</t>
   </si>
   <si>
-    <t>&lt;?TAX_REGIME_CODE?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD3?</t>
   </si>
   <si>
-    <t>&lt;?TAX_REGIME_NAME?&gt;</t>
-  </si>
-  <si>
     <t>AR</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD4?</t>
   </si>
   <si>
-    <t>&lt;?COUNTRY_CODE?&gt;</t>
-  </si>
-  <si>
     <t>1951-01-01T00:00:00.000+00:00</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD5?</t>
   </si>
   <si>
-    <t>&lt;?EFFECTIVE_FROM?&gt;</t>
-  </si>
-  <si>
     <t>EFFECTIVE_TO</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD6?</t>
   </si>
   <si>
-    <t>&lt;?EFFECTIVE_TO?&gt;</t>
-  </si>
-  <si>
     <t>ARS</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD7?</t>
   </si>
   <si>
-    <t>&lt;?TAX_CURRENCY_CODE?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD8?</t>
   </si>
   <si>
-    <t>&lt;?MINIMUM_ACCOUNTABLE_UNIT?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD9?</t>
   </si>
   <si>
-    <t>&lt;?TAX_PRECISION?&gt;</t>
-  </si>
-  <si>
     <t>NEAREST</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD10?</t>
   </si>
   <si>
-    <t>&lt;?ROUNDING_RULE_CODE?&gt;</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD11?</t>
   </si>
   <si>
-    <t>&lt;?ALLOW_ROUNDING_OVERRIDE_FLAG?&gt;</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD12?</t>
   </si>
   <si>
-    <t>&lt;?REGN_NUM_SAME_AS_LE_FLAG?&gt;</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD13?</t>
   </si>
   <si>
-    <t>&lt;?BUCKET_LEVEL_FLAG?&gt;</t>
-  </si>
-  <si>
     <t>VALIDATION_TYPE</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD14?</t>
   </si>
   <si>
-    <t>&lt;?VALIDATION_TYPE?&gt;</t>
-  </si>
-  <si>
     <t>VALIDATION_LEVEL</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD15?</t>
   </si>
   <si>
-    <t>&lt;?VALIDATION_LEVEL?&gt;</t>
-  </si>
-  <si>
     <t>UNIQUENESS_VALIDATION_LEVEL</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD16?</t>
   </si>
   <si>
-    <t>&lt;?UNIQUENESS_VALIDATION_LEVEL?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD17?</t>
   </si>
   <si>
-    <t>&lt;?CROSS_REGIME_COMPOUNDING_FLAG?&gt;</t>
-  </si>
-  <si>
     <t>REGIME_PRECEDENCE</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD18?</t>
-  </si>
-  <si>
-    <t>&lt;?REGIME_PRECEDENCE?&gt;</t>
   </si>
   <si>
     <t>Tax Regime Code</t>
@@ -361,24 +325,15 @@
     <t>XDO_?XDOFIELD21?</t>
   </si>
   <si>
-    <t>&lt;?CONTENT_OWNER_ID?&gt;</t>
-  </si>
-  <si>
     <t>RET GAN HONORARIOS PROF RI</t>
   </si>
   <si>
     <t>XDO_?XDOFIELD22?</t>
   </si>
   <si>
-    <t>&lt;?TAX?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD23?</t>
   </si>
   <si>
-    <t>&lt;?TAX_FULL_NAME?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD24?</t>
   </si>
   <si>
@@ -388,15 +343,9 @@
     <t>XDO_?XDOFIELD26?</t>
   </si>
   <si>
-    <t>&lt;?ALLOW_EXCEPTIONS_FLAG?&gt;</t>
-  </si>
-  <si>
     <t>XDO_?XDOFIELD27?</t>
   </si>
   <si>
-    <t>&lt;?ALLOW_EXEMPTIONS_FLAG?&gt;</t>
-  </si>
-  <si>
     <t>Configuration Owner</t>
   </si>
   <si>
@@ -421,10 +370,235 @@
     <t>&lt;xsl:for-each select=".//G_2"&gt;</t>
   </si>
   <si>
-    <t>REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830 REG RET GAN RG 830</t>
-  </si>
-  <si>
-    <t>1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00 1951-01-01T00:00:00.000+00:00</t>
+    <t>XDO_?XDOFIELD28?</t>
+  </si>
+  <si>
+    <t>RET GAN HONORARIOS RNI EST</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>RET GAN HONORARIOS RNI</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD29?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD30?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD31?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD32?</t>
+  </si>
+  <si>
+    <t>DEFAULT_FLG_EFFECTIVE_TO</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD33?</t>
+  </si>
+  <si>
+    <t>Default flag</t>
+  </si>
+  <si>
+    <t>Default Start Date</t>
+  </si>
+  <si>
+    <t>Default End Date</t>
+  </si>
+  <si>
+    <t>XDO_GROUP_?XDOG3?</t>
+  </si>
+  <si>
+    <t>&lt;xsl:for-each select=".//G_3"&gt;</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD34?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD35?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD36?</t>
+  </si>
+  <si>
+    <t>GAN HONORARIOS RNI</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD37?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD38?</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD39?</t>
+  </si>
+  <si>
+    <t>2023-09-30T00:00:00.000+00:00</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD40?</t>
+  </si>
+  <si>
+    <t>Tax Rate Type</t>
+  </si>
+  <si>
+    <t>PERCENTAGE</t>
+  </si>
+  <si>
+    <t>XDO_?XDOFIELD41?</t>
+  </si>
+  <si>
+    <t>XDO_GROUP_?XDOG4?</t>
+  </si>
+  <si>
+    <t>&lt;xsl:for-each select=".//G_4"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./COUNTRY_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_REGIME_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_REGIME_NAME?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./EFFECTIVE_FROM?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./EFFECTIVE_TO?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_CURRENCY_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./MINIMUM_ACCOUNTABLE_UNIT?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_PRECISION?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./ROUNDING_RULE_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./ALLOW_ROUNDING_OVERRIDE_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./REGN_NUM_SAME_AS_LE_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./BUCKET_LEVEL_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./VALIDATION_TYPE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./VALIDATION_LEVEL?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./UNIQUENESS_VALIDATION_LEVEL?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./CROSS_REGIME_COMPOUNDING_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./REGIME_PRECEDENCE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./CONTENT_OWNER_ID?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_FULL_NAME?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./ALLOW_EXCEPTIONS_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./ALLOW_EXEMPTIONS_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_STATUS_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./DEFAULT_STATUS_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./DEFAULT_FLG_EFFECTIVE_FROM?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./DEFAULT_FLG_EFFECTIVE_TO?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./TAX_RATE_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./DEFAULT_RATE_FLAG?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?./RATE_TYPE_CODE?&gt;</t>
+  </si>
+  <si>
+    <t>https://github.com/carakaki</t>
+  </si>
+  <si>
+    <t>RET GAN BIENES RI</t>
+  </si>
+  <si>
+    <t>RET GAN BIENES RNI</t>
+  </si>
+  <si>
+    <t>RET GAN CESION DE DER RI</t>
+  </si>
+  <si>
+    <t>RET GAN CESION DE DER RNI</t>
+  </si>
+  <si>
+    <t>RET GAN FLETES RI</t>
+  </si>
+  <si>
+    <t>RET GAN FLETES RNI PH</t>
+  </si>
+  <si>
+    <t>RET GAN FLETES RNI SOC</t>
+  </si>
+  <si>
+    <t>RET GAN HONORARIOS RI</t>
+  </si>
+  <si>
+    <t>RET GAN ALQUILERES RI</t>
+  </si>
+  <si>
+    <t>RET GAN ALQUILERES RNI PH</t>
+  </si>
+  <si>
+    <t>RET GAN ALQUILERES RNI SOC</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ BS MUEBLES RI</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ BS MUEBLES RNI PH</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ BS MUEBLES RNI SOC</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ RURALES RI</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ RURALES RNI PH</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ RURALES RNI SOC</t>
   </si>
   <si>
     <t>RET GAN HONORARIOS PROF RNI</t>
@@ -463,60 +637,6 @@
     <t>RET GAN DESP ADUANA RI</t>
   </si>
   <si>
-    <t>RET GAN ALQUILERES RI</t>
-  </si>
-  <si>
-    <t>RET GAN ALQUILERES RNI PH</t>
-  </si>
-  <si>
-    <t>RET GAN ALQUILERES RNI SOC</t>
-  </si>
-  <si>
-    <t>RET GAN ALQ BS MUEBLES RI</t>
-  </si>
-  <si>
-    <t>RET GAN ALQ BS MUEBLES RNI PH</t>
-  </si>
-  <si>
-    <t>RET GAN ALQ BS MUEBLES RNI SOC</t>
-  </si>
-  <si>
-    <t>RET GAN ALQ RURALES RI</t>
-  </si>
-  <si>
-    <t>RET GAN ALQ RURALES RNI PH</t>
-  </si>
-  <si>
-    <t>RET GAN ALQ RURALES RNI SOC</t>
-  </si>
-  <si>
-    <t>RET GAN BIENES RI</t>
-  </si>
-  <si>
-    <t>RET GAN BIENES RNI</t>
-  </si>
-  <si>
-    <t>RET GAN CESION DE DER RI</t>
-  </si>
-  <si>
-    <t>RET GAN CESION DE DER RNI</t>
-  </si>
-  <si>
-    <t>RET GAN FLETES RI</t>
-  </si>
-  <si>
-    <t>RET GAN FLETES RNI PH</t>
-  </si>
-  <si>
-    <t>RET GAN FLETES RNI SOC</t>
-  </si>
-  <si>
-    <t>RET GAN HONORARIOS RI</t>
-  </si>
-  <si>
-    <t>RET GAN HONORARIOS RNI</t>
-  </si>
-  <si>
     <t>RET GAN DESP ADUANA RNI</t>
   </si>
   <si>
@@ -563,6 +683,291 @@
   </si>
   <si>
     <t>RET GAN SERVICIOS RNI SOC</t>
+  </si>
+  <si>
+    <t>RET GAN BIENES RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN BIENES RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN CESION DE DER RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN CESION DE DER RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN FLETES RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN FLETES RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN FLETES RNI SOC EST</t>
+  </si>
+  <si>
+    <t>RET GAN HONORARIOS RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN HONORARIOS PROF RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQUILERES RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQUILERES RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQUILERES RNI SOC EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ BS MUEBLES RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ RURALES RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ RURALES RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN ALQ RURALES RNI SOC E</t>
+  </si>
+  <si>
+    <t>RET GAN HONORARIOS PROF RNI E</t>
+  </si>
+  <si>
+    <t>RET GAN INT FIN RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT FIN RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT NO FIN RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT NO FIN RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT NO FIN RNI SOC EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT ACC RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT ACC RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN INT ACC RNI SOC EST</t>
+  </si>
+  <si>
+    <t>RET GAN COMISIONES RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN COMISIONES RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN DESP ADUANA RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN DESP ADUANA RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN REGALIAS RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN REGALIAS RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN REGALIAS RNI SOC EST</t>
+  </si>
+  <si>
+    <t>RET GAN OBL NO HACER RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN OBL NO HACER RNI PH ES</t>
+  </si>
+  <si>
+    <t>RET GAN OBL NO HACER RNI SOC E</t>
+  </si>
+  <si>
+    <t>RET GAN TRAN LLAVE MARCA RI E</t>
+  </si>
+  <si>
+    <t>RET GAN TRAN LLAVE MARCA RNI E</t>
+  </si>
+  <si>
+    <t>RET GAN DER AUTOR RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN DER AUTOR RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN DIST PELICULAS RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN DIST PELICULAS RNI EST</t>
+  </si>
+  <si>
+    <t>RET GAN SERVICIOS RI EST</t>
+  </si>
+  <si>
+    <t>RET GAN SERVICIOS RNI PH EST</t>
+  </si>
+  <si>
+    <t>RET GAN SERVICIOS RNI SOC EST</t>
+  </si>
+  <si>
+    <t>GAN BIENES RI</t>
+  </si>
+  <si>
+    <t>GAN BIENES RNI</t>
+  </si>
+  <si>
+    <t>GAN CESION DE DER RI</t>
+  </si>
+  <si>
+    <t>GAN CESION DE DER RNI</t>
+  </si>
+  <si>
+    <t>GAN FLETES RI</t>
+  </si>
+  <si>
+    <t>GAN FLETES RNI PH</t>
+  </si>
+  <si>
+    <t>GAN FLETES RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN HONORARIOS RI</t>
+  </si>
+  <si>
+    <t>GROSS_AMT_SCHEDULE_RATE</t>
+  </si>
+  <si>
+    <t>GAN HONORARIOS PROF RI</t>
+  </si>
+  <si>
+    <t>2023-10-01T00:00:00.000+00:00</t>
+  </si>
+  <si>
+    <t>GAN ALQUILERES RI</t>
+  </si>
+  <si>
+    <t>GAN ALQUILERES RNI PH</t>
+  </si>
+  <si>
+    <t>GAN ALQUILERES RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN ALQ BS MUEBLES RI</t>
+  </si>
+  <si>
+    <t>GAN ALQ BS MUEBLES RNI PH</t>
+  </si>
+  <si>
+    <t>GAN ALQ BS MUEBLES RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN ALQ RURALES RI</t>
+  </si>
+  <si>
+    <t>GAN ALQ RURALES RNI PH</t>
+  </si>
+  <si>
+    <t>GAN ALQ RURALES RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN HONORARIOS PROF RNI</t>
+  </si>
+  <si>
+    <t>GAN INT FIN RI</t>
+  </si>
+  <si>
+    <t>GAN INT FIN RNI</t>
+  </si>
+  <si>
+    <t>GAN INT NO FIN RI</t>
+  </si>
+  <si>
+    <t>GAN INT NO FIN RNI PH</t>
+  </si>
+  <si>
+    <t>GAN INT NO FIN RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN INT ACC RI</t>
+  </si>
+  <si>
+    <t>GAN INT ACC RNI PH</t>
+  </si>
+  <si>
+    <t>GAN INT ACC RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN COMISIONES RI</t>
+  </si>
+  <si>
+    <t>GAN COMISIONES RNI</t>
+  </si>
+  <si>
+    <t>GAN DESP ADUANA RI</t>
+  </si>
+  <si>
+    <t>2026-10-06T00:00:00.000+00:00</t>
+  </si>
+  <si>
+    <t>GAN DESP ADUANA RI KOSDP-1773</t>
+  </si>
+  <si>
+    <t>2026-10-07T00:00:00.000+00:00</t>
+  </si>
+  <si>
+    <t>GAN DESP ADUANA RNI</t>
+  </si>
+  <si>
+    <t>GAN REGALIAS RI</t>
+  </si>
+  <si>
+    <t>GAN REGALIAS RNI PH</t>
+  </si>
+  <si>
+    <t>GAN REGALIAS RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN OBL NO HACER RI</t>
+  </si>
+  <si>
+    <t>GAN OBL NO HACER RNI PH</t>
+  </si>
+  <si>
+    <t>GAN OBL NO HACER RNI SOC</t>
+  </si>
+  <si>
+    <t>GAN TRAN LLAVE MARCA RI</t>
+  </si>
+  <si>
+    <t>GAN TRAN LLAVE MARCA RNI</t>
+  </si>
+  <si>
+    <t>GAN DER AUTOR RI</t>
+  </si>
+  <si>
+    <t>GAN DER AUTOR RNI</t>
+  </si>
+  <si>
+    <t>GAN DIST PELICULAS RI</t>
+  </si>
+  <si>
+    <t>GAN DIST PELICULAS RNI</t>
+  </si>
+  <si>
+    <t>GAN SERVICIOS RI</t>
+  </si>
+  <si>
+    <t>GAN SERVICIOS RNI PH</t>
+  </si>
+  <si>
+    <t>GAN SERVICIOS RNI SOC</t>
   </si>
 </sst>
 </file>
@@ -985,50 +1390,50 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30.0">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5">
-        <v>46314.0</v>
+        <v>46320.0</v>
       </c>
     </row>
   </sheetData>
@@ -1047,20 +1452,20 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B4" s="6"/>
     </row>
@@ -1081,84 +1486,84 @@
   <sheetData>
     <row r="1" spans="7:16">
       <c r="G1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="M1" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="P1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2">
         <v>0.01</v>
@@ -1167,22 +1572,22 @@
         <v>2.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="Q3" s="2"/>
     </row>
@@ -1198,1161 +1603,1161 @@
   <sheetData>
     <row r="1" spans="7:7">
       <c r="G1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2">
         <v>-99.0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2">
         <v>-99.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2">
         <v>-99.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2">
         <v>-99.0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2">
         <v>-99.0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2">
         <v>-99.0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
         <v>-99.0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2">
         <v>-99.0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2">
         <v>-99.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2">
         <v>-99.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
         <v>-99.0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2">
         <v>-99.0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2">
         <v>-99.0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2">
         <v>-99.0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>-99.0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2">
         <v>-99.0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
         <v>-99.0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2">
         <v>-99.0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2">
         <v>-99.0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2">
         <v>-99.0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2">
         <v>-99.0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2">
         <v>-99.0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>-99.0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2">
         <v>-99.0</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2">
         <v>-99.0</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2">
         <v>-99.0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" s="2">
         <v>-99.0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2">
         <v>-99.0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2">
         <v>-99.0</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2">
         <v>-99.0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2">
         <v>-99.0</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2">
         <v>-99.0</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2">
         <v>-99.0</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" s="2">
         <v>-99.0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" s="2">
         <v>-99.0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" s="2">
         <v>-99.0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="2">
         <v>-99.0</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="2">
         <v>-99.0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B41" s="2">
         <v>-99.0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" s="2">
         <v>-99.0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" s="2">
         <v>-99.0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B44" s="2">
         <v>-99.0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="2">
         <v>-99.0</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" s="2">
         <v>-99.0</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B47" s="2">
         <v>-99.0</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B48" s="2">
         <v>-99.0</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B49" s="2">
         <v>-99.0</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2362,7 +2767,2102 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A2:F49"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.285156" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:H51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.425781" customWidth="1"/>
@@ -2375,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
@@ -2389,7 +4889,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2417,7 +4917,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="10">
-        <v>46314.0</v>
+        <v>46320.0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2436,240 +4936,374 @@
     </row>
     <row r="11" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A12" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A13" s="14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A14" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A15" s="14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A16" s="14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A17" s="14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A18" s="14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="14" customFormat="1" ht="14.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
         <v>121</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B51" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
         <v>122</v>
       </c>
-      <c r="C39" t="s">
-        <v>94</v>
+      <c r="B52" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
